--- a/artfynd/A 24599-2022 artfynd.xlsx
+++ b/artfynd/A 24599-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79527877</v>
+        <v>95915538</v>
       </c>
       <c r="B2" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>1008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnsjö, Srm</t>
+          <t>Botkyrka, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667788.8829861149</v>
+        <v>667878</v>
       </c>
       <c r="R2" t="n">
-        <v>6561499.170698457</v>
+        <v>6561546</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-04-17</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-04-17</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +771,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sara Lundkvist</t>
+          <t>Charlotta Brandt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Lundkvist</t>
+          <t>Charlotta Brandt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,12 +786,7 @@
         <v>95915310</v>
       </c>
       <c r="B3" t="n">
-        <v>90282</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667876.7183671594</v>
+        <v>667877</v>
       </c>
       <c r="R3" t="n">
-        <v>6561548.737359084</v>
+        <v>6561548</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95915538</v>
+        <v>95915561</v>
       </c>
       <c r="B4" t="n">
-        <v>86860</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +902,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1008</v>
+        <v>4786</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Igelkottsröksvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycoperdon echinatum</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667878.862199205</v>
+        <v>667787</v>
       </c>
       <c r="R4" t="n">
-        <v>6561546.777874015</v>
+        <v>6561559</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,55 +999,61 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95899619</v>
+        <v>87018777</v>
       </c>
       <c r="B5" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>102021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Botkyrka, Srm</t>
+          <t>Kvarnsjöbacken, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>667803.117211119</v>
+        <v>667673</v>
       </c>
       <c r="R5" t="n">
-        <v>6561514.688148709</v>
+        <v>6561495</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2020-07-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2020-07-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,77 +1091,81 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Charlotta Brandt</t>
+          <t>Marlijn Sterenborg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Charlotta Brandt</t>
+          <t>Marlijn Sterenborg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118568175</v>
+        <v>118172530</v>
       </c>
       <c r="B6" t="n">
-        <v>42815</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>201122</v>
+        <v>102021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Almsnabbvinge</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Satyrium w-album</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Knoch, 1782)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sörmlandsleden Pålamalm, Srm</t>
+          <t>Sörmlandsleden N om Kvarnsjön, f.d. Kvarnsjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>667796</v>
+        <v>667766</v>
       </c>
       <c r="R6" t="n">
-        <v>6561540</v>
+        <v>6561482</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,12 +1192,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1223,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Stenfors</t>
+          <t>Christer Carlson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Stenfors</t>
+          <t>Christer Carlson, Maria Carlson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124897297</v>
+        <v>118172539</v>
       </c>
       <c r="B7" t="n">
-        <v>29251</v>
+        <v>43219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,26 +1246,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102690</v>
+        <v>201028</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartpälsbi</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthophora retusa</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1278,30 +1274,26 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>revirhävdande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>ca 150 m från bäcken vid  vägkant, Srm</t>
+          <t>Sörmlandsleden N om Kvarnsjön, f.d. Kvarnsjön, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>667886</v>
+        <v>667766</v>
       </c>
       <c r="R7" t="n">
-        <v>6561556</v>
+        <v>6561482</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,12 +1317,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,15 +1348,536 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Eneroth</t>
+          <t>Christer Carlson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Eneroth</t>
+          <t>Christer Carlson, Maria Carlson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118568175</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43328</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>201122</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Almsnabbvinge</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Satyrium w-album</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Knoch, 1782)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sörmlandsleden Pålamalm, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>667796</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6561540</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Martin Stenfors</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Martin Stenfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>87018768</v>
+      </c>
+      <c r="B9" t="n">
+        <v>45042</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>201164</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Zygaena filipendulae</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kvarnsjöbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>667673</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6561495</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>79527875</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kvarnsjö, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>667689</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6561506</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-04-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-04-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>79527877</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kvarnsjö, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>667789</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6561499</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-04-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-04-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>95899619</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>667803</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6561514</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Charlotta Brandt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Charlotta Brandt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24599-2022 artfynd.xlsx
+++ b/artfynd/A 24599-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95915538</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95915310</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95915561</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87018777</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118172530</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1357,6 +1387,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118172539</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,6 +1499,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568175</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1575,6 +1615,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87018768</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1672,6 +1717,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79527875</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1769,6 +1819,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79527877</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,8 +1933,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95899619</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>